--- a/netflix_movies.xlsx
+++ b/netflix_movies.xlsx
@@ -2665,10 +2665,10 @@
         <v>6.0345</v>
       </c>
       <c r="F66" t="n">
-        <v>6.798</v>
+        <v>6.796</v>
       </c>
       <c r="G66" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>1.913</v>
       </c>
       <c r="F68" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="G68" t="n">
         <v>21</v>
@@ -2804,7 +2804,7 @@
         <v>6.725</v>
       </c>
       <c r="G70" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         <v>34.8386</v>
       </c>
       <c r="F74" t="n">
-        <v>6.556</v>
+        <v>6.552</v>
       </c>
       <c r="G74" t="n">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -8815,10 +8815,10 @@
         <v>11.6423</v>
       </c>
       <c r="F247" t="n">
-        <v>6.897</v>
+        <v>6.904</v>
       </c>
       <c r="G247" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
